--- a/data/processed/green_harmonic_model.xlsx
+++ b/data/processed/green_harmonic_model.xlsx
@@ -2301,7 +2301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2334,17 +2334,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>harmonic_units_wan</t>
+          <t>harmonic_cogs_bn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>130</v>
+        <v>0.754</v>
       </c>
       <c r="C2" t="n">
-        <v>180</v>
+        <v>1.008</v>
       </c>
       <c r="D2" t="n">
-        <v>250</v>
+        <v>1.35</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2355,17 +2355,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>joint_units_wan</t>
+          <t>harmonic_revenue_bn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>1.495</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>1.98</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>2.625</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2376,17 +2376,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>revenue_bn</t>
+          <t>harmonic_units_wan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.975</v>
+        <v>130</v>
       </c>
       <c r="C4" t="n">
-        <v>3.08</v>
+        <v>180</v>
       </c>
       <c r="D4" t="n">
-        <v>4.625</v>
+        <v>250</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cogs_bn</t>
+          <t>joint_cogs_bn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.044</v>
+        <v>0.29</v>
       </c>
       <c r="C5" t="n">
-        <v>1.683</v>
+        <v>0.675</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2418,17 +2418,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gross_profit_bn</t>
+          <t>joint_revenue_bn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.931</v>
+        <v>0.48</v>
       </c>
       <c r="C6" t="n">
-        <v>1.397</v>
+        <v>1.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.025</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2439,17 +2439,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gross_margin</t>
+          <t>joint_units_wan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.47139241</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>0.45357143</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>0.43783784</v>
+        <v>100</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2460,17 +2460,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>opex_bn</t>
+          <t>revenue_bn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.41475</v>
+        <v>1.975</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6468</v>
+        <v>3.08</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9712499999999999</v>
+        <v>4.625</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2481,17 +2481,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ebitda_bn</t>
+          <t>cogs_bn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.51625</v>
+        <v>1.044</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7502</v>
+        <v>1.683</v>
       </c>
       <c r="D9" t="n">
-        <v>1.05375</v>
+        <v>2.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2502,17 +2502,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ebitda_margin</t>
+          <t>gross_profit_bn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.26139241</v>
+        <v>0.931</v>
       </c>
       <c r="C10" t="n">
-        <v>0.24357143</v>
+        <v>1.397</v>
       </c>
       <c r="D10" t="n">
-        <v>0.22783784</v>
+        <v>2.025</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2523,17 +2523,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ebit_bn</t>
+          <t>gross_margin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.457</v>
+        <v>0.47139241</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.45357143</v>
       </c>
       <c r="D11" t="n">
-        <v>0.915</v>
+        <v>0.43783784</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2544,17 +2544,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tax_bn</t>
+          <t>opex_bn</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.11425</v>
+        <v>0.41475</v>
       </c>
       <c r="C12" t="n">
-        <v>0.16445</v>
+        <v>0.6468</v>
       </c>
       <c r="D12" t="n">
-        <v>0.22875</v>
+        <v>0.9712499999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2565,17 +2565,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>capex_bn</t>
+          <t>ebitda_bn</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1185</v>
+        <v>0.51625</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1848</v>
+        <v>0.7502</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2775</v>
+        <v>1.05375</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2586,17 +2586,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>change_nwc_bn</t>
+          <t>ebitda_margin</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09875</v>
+        <v>0.26139241</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05525</v>
+        <v>0.24357143</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07725</v>
+        <v>0.22783784</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2607,19 +2607,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fcf_bn</t>
+          <t>ebit_bn</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.18475</v>
+        <v>0.457</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3457</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.47025</v>
+        <v>0.915</v>
       </c>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tax_bn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.11425</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.16445</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.22875</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>calculated; see src/financial_model.py</t>
         </is>
@@ -2628,15 +2649,78 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>capex_bn</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1848</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>change_nwc_bn</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.09875</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.05525</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.07725</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fcf_bn</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.18475</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.47025</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>enterprise_value_bn</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B21" t="n">
         <v>6.00560508</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>DCF</t>
         </is>
@@ -2653,7 +2737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2686,17 +2770,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>harmonic_units_wan</t>
+          <t>harmonic_cogs_bn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>143</v>
+        <v>0.804518</v>
       </c>
       <c r="C2" t="n">
-        <v>198</v>
+        <v>1.075536</v>
       </c>
       <c r="D2" t="n">
-        <v>275</v>
+        <v>1.44045</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2707,17 +2791,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>joint_units_wan</t>
+          <t>harmonic_revenue_bn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>1.693835</v>
       </c>
       <c r="C3" t="n">
-        <v>55</v>
+        <v>2.24334</v>
       </c>
       <c r="D3" t="n">
-        <v>110</v>
+        <v>2.974125</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2728,17 +2812,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>revenue_bn</t>
+          <t>harmonic_units_wan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.237675</v>
+        <v>143</v>
       </c>
       <c r="C4" t="n">
-        <v>3.48964</v>
+        <v>198</v>
       </c>
       <c r="D4" t="n">
-        <v>5.240125</v>
+        <v>275</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2749,17 +2833,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cogs_bn</t>
+          <t>joint_cogs_bn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.113948</v>
+        <v>0.30943</v>
       </c>
       <c r="C5" t="n">
-        <v>1.795761</v>
+        <v>0.720225</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7742</v>
+        <v>1.33375</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2770,17 +2854,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gross_profit_bn</t>
+          <t>joint_revenue_bn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.123727</v>
+        <v>0.54384</v>
       </c>
       <c r="C6" t="n">
-        <v>1.693879</v>
+        <v>1.2463</v>
       </c>
       <c r="D6" t="n">
-        <v>2.465925</v>
+        <v>2.266</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2791,17 +2875,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gross_margin</t>
+          <t>joint_units_wan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.50218508</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>0.48540222</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
-        <v>0.47058515</v>
+        <v>110</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2812,17 +2896,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>opex_bn</t>
+          <t>revenue_bn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.46051351</v>
+        <v>2.237675</v>
       </c>
       <c r="C8" t="n">
-        <v>0.71816791</v>
+        <v>3.48964</v>
       </c>
       <c r="D8" t="n">
-        <v>1.07841772</v>
+        <v>5.240125</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2833,17 +2917,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ebitda_bn</t>
+          <t>cogs_bn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.66321348</v>
+        <v>1.113948</v>
       </c>
       <c r="C9" t="n">
-        <v>0.97571109</v>
+        <v>1.795761</v>
       </c>
       <c r="D9" t="n">
-        <v>1.38750728</v>
+        <v>2.7742</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2854,17 +2938,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ebitda_margin</t>
+          <t>gross_profit_bn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.29638508</v>
+        <v>1.123727</v>
       </c>
       <c r="C10" t="n">
-        <v>0.27960222</v>
+        <v>1.693879</v>
       </c>
       <c r="D10" t="n">
-        <v>0.26478515</v>
+        <v>2.465925</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2875,17 +2959,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ebit_bn</t>
+          <t>gross_margin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.59608323</v>
+        <v>0.50218508</v>
       </c>
       <c r="C11" t="n">
-        <v>0.87102189</v>
+        <v>0.48540222</v>
       </c>
       <c r="D11" t="n">
-        <v>1.23030353</v>
+        <v>0.47058515</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2896,17 +2980,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tax_bn</t>
+          <t>opex_bn</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.14902081</v>
+        <v>0.46051351</v>
       </c>
       <c r="C12" t="n">
-        <v>0.21775547</v>
+        <v>0.71816791</v>
       </c>
       <c r="D12" t="n">
-        <v>0.30757588</v>
+        <v>1.07841772</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2917,17 +3001,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>capex_bn</t>
+          <t>ebitda_bn</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1342605</v>
+        <v>0.66321348</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2093784</v>
+        <v>0.97571109</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3144075</v>
+        <v>1.38750728</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2938,17 +3022,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>change_nwc_bn</t>
+          <t>ebitda_margin</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.11188375</v>
+        <v>0.29638508</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06259824999999999</v>
+        <v>0.27960222</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08752425</v>
+        <v>0.26478515</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2959,19 +3043,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fcf_bn</t>
+          <t>ebit_bn</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.26804843</v>
+        <v>0.59608323</v>
       </c>
       <c r="C15" t="n">
-        <v>0.48597897</v>
+        <v>0.87102189</v>
       </c>
       <c r="D15" t="n">
-        <v>0.67799964</v>
+        <v>1.23030353</v>
       </c>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tax_bn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.14902081</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.21775547</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.30757588</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>calculated; see src/financial_model.py</t>
         </is>
@@ -2980,15 +3085,78 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>capex_bn</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1342605</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.2093784</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3144075</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>change_nwc_bn</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.11188375</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.06259824999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.08752425</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fcf_bn</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.26804843</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.48597897</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.67799964</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>enterprise_value_bn</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B21" t="n">
         <v>8.65003424</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>DCF</t>
         </is>
@@ -3005,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3038,17 +3206,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>harmonic_units_wan</t>
+          <t>harmonic_cogs_bn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117</v>
+        <v>0.71253</v>
       </c>
       <c r="C2" t="n">
-        <v>162</v>
+        <v>0.95256</v>
       </c>
       <c r="D2" t="n">
-        <v>225</v>
+        <v>1.27575</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3059,17 +3227,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>joint_units_wan</t>
+          <t>harmonic_revenue_bn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>1.305135</v>
       </c>
       <c r="C3" t="n">
-        <v>45</v>
+        <v>1.72854</v>
       </c>
       <c r="D3" t="n">
-        <v>90</v>
+        <v>2.291625</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3080,17 +3248,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>revenue_bn</t>
+          <t>harmonic_units_wan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.724175</v>
+        <v>117</v>
       </c>
       <c r="C4" t="n">
-        <v>2.68884</v>
+        <v>162</v>
       </c>
       <c r="D4" t="n">
-        <v>4.037625</v>
+        <v>225</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3101,17 +3269,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cogs_bn</t>
+          <t>joint_cogs_bn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.98658</v>
+        <v>0.27405</v>
       </c>
       <c r="C5" t="n">
-        <v>1.590435</v>
+        <v>0.637875</v>
       </c>
       <c r="D5" t="n">
-        <v>2.457</v>
+        <v>1.18125</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3122,17 +3290,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gross_profit_bn</t>
+          <t>joint_revenue_bn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.737595</v>
+        <v>0.41904</v>
       </c>
       <c r="C6" t="n">
-        <v>1.098405</v>
+        <v>0.9603</v>
       </c>
       <c r="D6" t="n">
-        <v>1.580625</v>
+        <v>1.746</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3143,17 +3311,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gross_margin</t>
+          <t>joint_units_wan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4277959</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.40850515</v>
+        <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>0.39147395</v>
+        <v>90</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3164,17 +3332,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>opex_bn</t>
+          <t>revenue_bn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.37293905</v>
+        <v>1.724175</v>
       </c>
       <c r="C8" t="n">
-        <v>0.58159609</v>
+        <v>2.68884</v>
       </c>
       <c r="D8" t="n">
-        <v>0.87333829</v>
+        <v>4.037625</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3185,17 +3353,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ebitda_bn</t>
+          <t>cogs_bn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.36465595</v>
+        <v>0.98658</v>
       </c>
       <c r="C9" t="n">
-        <v>0.51680891</v>
+        <v>1.590435</v>
       </c>
       <c r="D9" t="n">
-        <v>0.70728671</v>
+        <v>2.457</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3206,17 +3374,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ebitda_margin</t>
+          <t>gross_profit_bn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2114959</v>
+        <v>0.737595</v>
       </c>
       <c r="C10" t="n">
-        <v>0.19220515</v>
+        <v>1.098405</v>
       </c>
       <c r="D10" t="n">
-        <v>0.17517395</v>
+        <v>1.580625</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3227,17 +3395,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ebit_bn</t>
+          <t>gross_margin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3129307</v>
+        <v>0.4277959</v>
       </c>
       <c r="C11" t="n">
-        <v>0.43614371</v>
+        <v>0.40850515</v>
       </c>
       <c r="D11" t="n">
-        <v>0.58615796</v>
+        <v>0.39147395</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3248,17 +3416,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tax_bn</t>
+          <t>opex_bn</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07823267</v>
+        <v>0.37293905</v>
       </c>
       <c r="C12" t="n">
-        <v>0.10903593</v>
+        <v>0.58159609</v>
       </c>
       <c r="D12" t="n">
-        <v>0.14653949</v>
+        <v>0.87333829</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3269,17 +3437,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>capex_bn</t>
+          <t>ebitda_bn</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1034505</v>
+        <v>0.36465595</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1613304</v>
+        <v>0.51680891</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2422575</v>
+        <v>0.70728671</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3290,17 +3458,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>change_nwc_bn</t>
+          <t>ebitda_margin</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08620875</v>
+        <v>0.2114959</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04823325</v>
+        <v>0.19220515</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06743925000000001</v>
+        <v>0.17517395</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3311,19 +3479,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fcf_bn</t>
+          <t>ebit_bn</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09676402000000001</v>
+        <v>0.3129307</v>
       </c>
       <c r="C15" t="n">
-        <v>0.19820933</v>
+        <v>0.43614371</v>
       </c>
       <c r="D15" t="n">
-        <v>0.25105047</v>
+        <v>0.58615796</v>
       </c>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tax_bn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.07823267</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.10903593</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.14653949</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>calculated; see src/financial_model.py</t>
         </is>
@@ -3332,15 +3521,78 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>capex_bn</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1034505</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1613304</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2422575</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>change_nwc_bn</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.08620875</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.04823325</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.06743925000000001</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fcf_bn</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.09676402000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.19820933</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.25105047</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>calculated; see src/financial_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>enterprise_value_bn</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B21" t="n">
         <v>3.21577278</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>DCF</t>
         </is>
